--- a/artfynd/A 50533-2023 artfynd.xlsx
+++ b/artfynd/A 50533-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113711378</v>
+        <v>113711368</v>
       </c>
       <c r="B2" t="n">
-        <v>91402</v>
+        <v>56826</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4366</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>633994</v>
+        <v>634097</v>
       </c>
       <c r="R2" t="n">
-        <v>7043512</v>
+        <v>7043390</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -753,13 +753,17 @@
           <t>2023-09-09</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Hane i sitt födosöksområde</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -782,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113711364</v>
+        <v>113711371</v>
       </c>
       <c r="B3" t="n">
-        <v>56955</v>
+        <v>78236</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>634047</v>
+        <v>634062</v>
       </c>
       <c r="R3" t="n">
-        <v>7043456</v>
+        <v>7043422</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -858,11 +862,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-09-09</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>I sitt häckningsrevir</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113711371</v>
+        <v>113711369</v>
       </c>
       <c r="B4" t="n">
-        <v>78236</v>
+        <v>79265</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -933,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>634062</v>
+        <v>634071</v>
       </c>
       <c r="R4" t="n">
-        <v>7043422</v>
+        <v>7043394</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -969,6 +968,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-09-09</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På stambasen av en sälg</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113711376</v>
+        <v>113711375</v>
       </c>
       <c r="B5" t="n">
-        <v>78794</v>
+        <v>56021</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1015,21 +1019,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>102612</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1039,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>633976</v>
+        <v>634006</v>
       </c>
       <c r="R5" t="n">
-        <v>7043552</v>
+        <v>7043583</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1075,6 +1079,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-09-09</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ett par i sitt revir</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1105,10 +1114,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113711367</v>
+        <v>113711373</v>
       </c>
       <c r="B6" t="n">
-        <v>97398</v>
+        <v>81944</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1117,25 +1126,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1145,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>634099</v>
+        <v>634031</v>
       </c>
       <c r="R6" t="n">
-        <v>7043362</v>
+        <v>7043487</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1181,11 +1190,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-09-09</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ett tjugotal plantor</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1216,10 +1220,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113711370</v>
+        <v>113711377</v>
       </c>
       <c r="B7" t="n">
-        <v>91406</v>
+        <v>91382</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1232,21 +1236,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1256,10 +1260,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>634063</v>
+        <v>633998</v>
       </c>
       <c r="R7" t="n">
-        <v>7043421</v>
+        <v>7043532</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1292,6 +1296,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-09-09</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Flertal fruktkroppar</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1322,10 +1331,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113711365</v>
+        <v>113711374</v>
       </c>
       <c r="B8" t="n">
-        <v>81944</v>
+        <v>79199</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1334,25 +1343,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>6456</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1362,10 +1371,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>634113</v>
+        <v>634019</v>
       </c>
       <c r="R8" t="n">
-        <v>7043339</v>
+        <v>7043512</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1398,6 +1407,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-09-09</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1428,10 +1442,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113711379</v>
+        <v>113711376</v>
       </c>
       <c r="B9" t="n">
-        <v>91406</v>
+        <v>78794</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1444,21 +1458,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2059</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1468,10 +1482,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>633985</v>
+        <v>633976</v>
       </c>
       <c r="R9" t="n">
-        <v>7043541</v>
+        <v>7043552</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1534,10 +1548,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113711377</v>
+        <v>113711372</v>
       </c>
       <c r="B10" t="n">
-        <v>91382</v>
+        <v>97398</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1546,25 +1560,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4361</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1574,10 +1588,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>633998</v>
+        <v>634025</v>
       </c>
       <c r="R10" t="n">
-        <v>7043532</v>
+        <v>7043472</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1614,7 +1628,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Flertal fruktkroppar</t>
+          <t>Ett femtiotal plantor</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1645,10 +1659,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113711366</v>
+        <v>113711370</v>
       </c>
       <c r="B11" t="n">
-        <v>90327</v>
+        <v>91406</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1657,25 +1671,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1106</v>
+        <v>2059</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1685,10 +1699,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>634106</v>
+        <v>634063</v>
       </c>
       <c r="R11" t="n">
-        <v>7043344</v>
+        <v>7043421</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1721,11 +1735,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-09-09</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1756,10 +1765,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113711368</v>
+        <v>113711379</v>
       </c>
       <c r="B12" t="n">
-        <v>56826</v>
+        <v>91406</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1772,21 +1781,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>2059</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1796,10 +1805,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>634097</v>
+        <v>633985</v>
       </c>
       <c r="R12" t="n">
-        <v>7043390</v>
+        <v>7043541</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1832,11 +1841,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-09-09</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Hane i sitt födosöksområde</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1867,10 +1871,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113711375</v>
+        <v>113711366</v>
       </c>
       <c r="B13" t="n">
-        <v>56021</v>
+        <v>90327</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1879,25 +1883,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102612</v>
+        <v>1106</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1907,10 +1911,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>634006</v>
+        <v>634106</v>
       </c>
       <c r="R13" t="n">
-        <v>7043583</v>
+        <v>7043344</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1947,7 +1951,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ett par i sitt revir</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1978,10 +1982,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113711369</v>
+        <v>113711364</v>
       </c>
       <c r="B14" t="n">
-        <v>79265</v>
+        <v>56955</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1994,21 +1998,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2018,10 +2022,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>634071</v>
+        <v>634047</v>
       </c>
       <c r="R14" t="n">
-        <v>7043394</v>
+        <v>7043456</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2058,7 +2062,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På stambasen av en sälg</t>
+          <t>I sitt häckningsrevir</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2089,10 +2093,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113711373</v>
+        <v>113711367</v>
       </c>
       <c r="B15" t="n">
-        <v>81944</v>
+        <v>97398</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2101,25 +2105,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2129,10 +2133,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>634031</v>
+        <v>634099</v>
       </c>
       <c r="R15" t="n">
-        <v>7043487</v>
+        <v>7043362</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2165,6 +2169,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-09-09</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ett tjugotal plantor</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2195,10 +2204,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113711374</v>
+        <v>113711365</v>
       </c>
       <c r="B16" t="n">
-        <v>79199</v>
+        <v>81944</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2207,25 +2216,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6456</v>
+        <v>1312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2235,10 +2244,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>634019</v>
+        <v>634113</v>
       </c>
       <c r="R16" t="n">
-        <v>7043512</v>
+        <v>7043339</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2271,11 +2280,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-09-09</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2306,10 +2310,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113711372</v>
+        <v>113711378</v>
       </c>
       <c r="B17" t="n">
-        <v>97398</v>
+        <v>91402</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2318,25 +2322,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>4366</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2346,10 +2350,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>634025</v>
+        <v>633994</v>
       </c>
       <c r="R17" t="n">
-        <v>7043472</v>
+        <v>7043512</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2384,17 +2388,13 @@
           <t>2023-09-09</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ett femtiotal plantor</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 50533-2023 artfynd.xlsx
+++ b/artfynd/A 50533-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113711368</v>
+        <v>113711365</v>
       </c>
       <c r="B2" t="n">
-        <v>56826</v>
+        <v>81944</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>634097</v>
+        <v>634113</v>
       </c>
       <c r="R2" t="n">
-        <v>7043390</v>
+        <v>7043339</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-09-09</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Hane i sitt födosöksområde</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113711371</v>
+        <v>113711366</v>
       </c>
       <c r="B3" t="n">
-        <v>78236</v>
+        <v>90331</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>185</v>
+        <v>1106</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>634062</v>
+        <v>634106</v>
       </c>
       <c r="R3" t="n">
-        <v>7043422</v>
+        <v>7043344</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -862,6 +857,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-09-09</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113711369</v>
+        <v>113711374</v>
       </c>
       <c r="B4" t="n">
-        <v>79265</v>
+        <v>79199</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,25 +904,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>634071</v>
+        <v>634019</v>
       </c>
       <c r="R4" t="n">
-        <v>7043394</v>
+        <v>7043512</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -972,7 +972,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På stambasen av en sälg</t>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113711375</v>
+        <v>113711368</v>
       </c>
       <c r="B5" t="n">
-        <v>56021</v>
+        <v>56826</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1019,16 +1019,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1043,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>634006</v>
+        <v>634097</v>
       </c>
       <c r="R5" t="n">
-        <v>7043583</v>
+        <v>7043390</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ett par i sitt revir</t>
+          <t>Hane i sitt födosöksområde</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1114,10 +1114,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113711373</v>
+        <v>113711370</v>
       </c>
       <c r="B6" t="n">
-        <v>81944</v>
+        <v>91410</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1130,21 +1130,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>2059</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>634031</v>
+        <v>634063</v>
       </c>
       <c r="R6" t="n">
-        <v>7043487</v>
+        <v>7043421</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1220,10 +1220,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113711377</v>
+        <v>113711378</v>
       </c>
       <c r="B7" t="n">
-        <v>91382</v>
+        <v>91406</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1232,25 +1232,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4361</v>
+        <v>4366</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1260,10 +1260,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>633998</v>
+        <v>633994</v>
       </c>
       <c r="R7" t="n">
-        <v>7043532</v>
+        <v>7043512</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1298,17 +1298,13 @@
           <t>2023-09-09</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Flertal fruktkroppar</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1331,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113711374</v>
+        <v>113711379</v>
       </c>
       <c r="B8" t="n">
-        <v>79199</v>
+        <v>91410</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1343,25 +1339,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6456</v>
+        <v>2059</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1371,10 +1367,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>634019</v>
+        <v>633985</v>
       </c>
       <c r="R8" t="n">
-        <v>7043512</v>
+        <v>7043541</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1407,11 +1403,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-09-09</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1442,10 +1433,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113711376</v>
+        <v>113711364</v>
       </c>
       <c r="B9" t="n">
-        <v>78794</v>
+        <v>56955</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1458,21 +1449,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1482,10 +1473,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>633976</v>
+        <v>634047</v>
       </c>
       <c r="R9" t="n">
-        <v>7043552</v>
+        <v>7043456</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1518,6 +1509,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-09-09</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>I sitt häckningsrevir</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1548,10 +1544,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113711372</v>
+        <v>113711369</v>
       </c>
       <c r="B10" t="n">
-        <v>97398</v>
+        <v>79265</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1560,25 +1556,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1588,10 +1584,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>634025</v>
+        <v>634071</v>
       </c>
       <c r="R10" t="n">
-        <v>7043472</v>
+        <v>7043394</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1628,7 +1624,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ett femtiotal plantor</t>
+          <t>På stambasen av en sälg</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1659,10 +1655,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113711370</v>
+        <v>113711367</v>
       </c>
       <c r="B11" t="n">
-        <v>91406</v>
+        <v>97402</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1671,25 +1667,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2059</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1699,10 +1695,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>634063</v>
+        <v>634099</v>
       </c>
       <c r="R11" t="n">
-        <v>7043421</v>
+        <v>7043362</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1735,6 +1731,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-09-09</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ett tjugotal plantor</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1765,10 +1766,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113711379</v>
+        <v>113711372</v>
       </c>
       <c r="B12" t="n">
-        <v>91406</v>
+        <v>97402</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1777,25 +1778,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2059</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1805,10 +1806,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>633985</v>
+        <v>634025</v>
       </c>
       <c r="R12" t="n">
-        <v>7043541</v>
+        <v>7043472</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1841,6 +1842,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-09-09</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ett femtiotal plantor</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1871,10 +1877,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113711366</v>
+        <v>113711375</v>
       </c>
       <c r="B13" t="n">
-        <v>90327</v>
+        <v>56021</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1883,25 +1889,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1106</v>
+        <v>102612</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1911,10 +1917,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>634106</v>
+        <v>634006</v>
       </c>
       <c r="R13" t="n">
-        <v>7043344</v>
+        <v>7043583</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1951,7 +1957,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>Ett par i sitt revir</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1982,10 +1988,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113711364</v>
+        <v>113711373</v>
       </c>
       <c r="B14" t="n">
-        <v>56955</v>
+        <v>81944</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1998,21 +2004,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2022,10 +2028,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>634047</v>
+        <v>634031</v>
       </c>
       <c r="R14" t="n">
-        <v>7043456</v>
+        <v>7043487</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2058,11 +2064,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-09-09</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>I sitt häckningsrevir</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2093,10 +2094,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113711367</v>
+        <v>113711376</v>
       </c>
       <c r="B15" t="n">
-        <v>97398</v>
+        <v>78794</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2105,25 +2106,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2133,10 +2134,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>634099</v>
+        <v>633976</v>
       </c>
       <c r="R15" t="n">
-        <v>7043362</v>
+        <v>7043552</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2169,11 +2170,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-09-09</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ett tjugotal plantor</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2204,10 +2200,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113711365</v>
+        <v>113711371</v>
       </c>
       <c r="B16" t="n">
-        <v>81944</v>
+        <v>78236</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2220,21 +2216,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>185</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2244,10 +2240,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>634113</v>
+        <v>634062</v>
       </c>
       <c r="R16" t="n">
-        <v>7043339</v>
+        <v>7043422</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2310,10 +2306,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113711378</v>
+        <v>113711377</v>
       </c>
       <c r="B17" t="n">
-        <v>91402</v>
+        <v>91386</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2322,25 +2318,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4366</v>
+        <v>4361</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2350,10 +2346,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>633994</v>
+        <v>633998</v>
       </c>
       <c r="R17" t="n">
-        <v>7043512</v>
+        <v>7043532</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2388,13 +2384,17 @@
           <t>2023-09-09</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Flertal fruktkroppar</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 50533-2023 artfynd.xlsx
+++ b/artfynd/A 50533-2023 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113711366</v>
+        <v>113711369</v>
       </c>
       <c r="B3" t="n">
-        <v>90331</v>
+        <v>79265</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1106</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>634106</v>
+        <v>634071</v>
       </c>
       <c r="R3" t="n">
-        <v>7043344</v>
+        <v>7043394</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På stambasen av en sälg</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113711374</v>
+        <v>113711367</v>
       </c>
       <c r="B4" t="n">
-        <v>79199</v>
+        <v>97402</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,25 +904,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>634019</v>
+        <v>634099</v>
       </c>
       <c r="R4" t="n">
-        <v>7043512</v>
+        <v>7043362</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -972,7 +972,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På asp</t>
+          <t>Ett tjugotal plantor</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113711368</v>
+        <v>113711370</v>
       </c>
       <c r="B5" t="n">
-        <v>56826</v>
+        <v>91410</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1019,21 +1019,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>2059</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1043,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>634097</v>
+        <v>634063</v>
       </c>
       <c r="R5" t="n">
-        <v>7043390</v>
+        <v>7043421</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1079,11 +1079,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-09-09</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Hane i sitt födosöksområde</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1114,10 +1109,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113711370</v>
+        <v>113711373</v>
       </c>
       <c r="B6" t="n">
-        <v>91410</v>
+        <v>81944</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1130,21 +1125,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2059</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1154,10 +1149,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>634063</v>
+        <v>634031</v>
       </c>
       <c r="R6" t="n">
-        <v>7043421</v>
+        <v>7043487</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1220,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113711378</v>
+        <v>113711364</v>
       </c>
       <c r="B7" t="n">
-        <v>91406</v>
+        <v>56955</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1232,25 +1227,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4366</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1260,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>633994</v>
+        <v>634047</v>
       </c>
       <c r="R7" t="n">
-        <v>7043512</v>
+        <v>7043456</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1298,13 +1293,17 @@
           <t>2023-09-09</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>I sitt häckningsrevir</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1327,10 +1326,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113711379</v>
+        <v>113711376</v>
       </c>
       <c r="B8" t="n">
-        <v>91410</v>
+        <v>78794</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1343,21 +1342,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2059</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1367,10 +1366,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>633985</v>
+        <v>633976</v>
       </c>
       <c r="R8" t="n">
-        <v>7043541</v>
+        <v>7043552</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1433,10 +1432,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113711364</v>
+        <v>113711377</v>
       </c>
       <c r="B9" t="n">
-        <v>56955</v>
+        <v>91386</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1449,21 +1448,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>4361</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1473,10 +1472,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>634047</v>
+        <v>633998</v>
       </c>
       <c r="R9" t="n">
-        <v>7043456</v>
+        <v>7043532</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1513,7 +1512,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>I sitt häckningsrevir</t>
+          <t>Flertal fruktkroppar</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1544,10 +1543,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113711369</v>
+        <v>113711368</v>
       </c>
       <c r="B10" t="n">
-        <v>79265</v>
+        <v>56826</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1560,21 +1559,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1584,10 +1583,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>634071</v>
+        <v>634097</v>
       </c>
       <c r="R10" t="n">
-        <v>7043394</v>
+        <v>7043390</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1624,7 +1623,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På stambasen av en sälg</t>
+          <t>Hane i sitt födosöksområde</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1655,10 +1654,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113711367</v>
+        <v>113711371</v>
       </c>
       <c r="B11" t="n">
-        <v>97402</v>
+        <v>78236</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1667,25 +1666,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1695,10 +1694,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>634099</v>
+        <v>634062</v>
       </c>
       <c r="R11" t="n">
-        <v>7043362</v>
+        <v>7043422</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1731,11 +1730,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-09-09</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ett tjugotal plantor</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1766,10 +1760,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113711372</v>
+        <v>113711375</v>
       </c>
       <c r="B12" t="n">
-        <v>97402</v>
+        <v>56021</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1778,25 +1772,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1806,10 +1800,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>634025</v>
+        <v>634006</v>
       </c>
       <c r="R12" t="n">
-        <v>7043472</v>
+        <v>7043583</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1846,7 +1840,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ett femtiotal plantor</t>
+          <t>Ett par i sitt revir</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1877,10 +1871,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113711375</v>
+        <v>113711379</v>
       </c>
       <c r="B13" t="n">
-        <v>56021</v>
+        <v>91410</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1893,21 +1887,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102612</v>
+        <v>2059</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1917,10 +1911,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>634006</v>
+        <v>633985</v>
       </c>
       <c r="R13" t="n">
-        <v>7043583</v>
+        <v>7043541</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1953,11 +1947,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-09-09</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ett par i sitt revir</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1988,10 +1977,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113711373</v>
+        <v>113711366</v>
       </c>
       <c r="B14" t="n">
-        <v>81944</v>
+        <v>90331</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2000,25 +1989,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>1106</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2028,10 +2017,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>634031</v>
+        <v>634106</v>
       </c>
       <c r="R14" t="n">
-        <v>7043487</v>
+        <v>7043344</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2064,6 +2053,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-09-09</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2094,10 +2088,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113711376</v>
+        <v>113711378</v>
       </c>
       <c r="B15" t="n">
-        <v>78794</v>
+        <v>91406</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2106,25 +2100,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>4366</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2134,10 +2128,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>633976</v>
+        <v>633994</v>
       </c>
       <c r="R15" t="n">
-        <v>7043552</v>
+        <v>7043512</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2178,6 +2172,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2200,10 +2195,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113711371</v>
+        <v>113711372</v>
       </c>
       <c r="B16" t="n">
-        <v>78236</v>
+        <v>97402</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2212,25 +2207,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2240,10 +2235,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>634062</v>
+        <v>634025</v>
       </c>
       <c r="R16" t="n">
-        <v>7043422</v>
+        <v>7043472</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2276,6 +2271,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-09-09</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ett femtiotal plantor</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2306,10 +2306,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113711377</v>
+        <v>113711374</v>
       </c>
       <c r="B17" t="n">
-        <v>91386</v>
+        <v>79199</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2318,25 +2318,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4361</v>
+        <v>6456</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2346,10 +2346,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>633998</v>
+        <v>634019</v>
       </c>
       <c r="R17" t="n">
-        <v>7043532</v>
+        <v>7043512</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Flertal fruktkroppar</t>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 50533-2023 artfynd.xlsx
+++ b/artfynd/A 50533-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113711365</v>
+        <v>113711372</v>
       </c>
       <c r="B2" t="n">
-        <v>81944</v>
+        <v>97402</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>634113</v>
+        <v>634025</v>
       </c>
       <c r="R2" t="n">
-        <v>7043339</v>
+        <v>7043472</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-09-09</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ett femtiotal plantor</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113711369</v>
+        <v>113711365</v>
       </c>
       <c r="B3" t="n">
-        <v>79265</v>
+        <v>81944</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>634071</v>
+        <v>634113</v>
       </c>
       <c r="R3" t="n">
-        <v>7043394</v>
+        <v>7043339</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -857,11 +862,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-09-09</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På stambasen av en sälg</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113711367</v>
+        <v>113711377</v>
       </c>
       <c r="B4" t="n">
-        <v>97402</v>
+        <v>91386</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,25 +904,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>634099</v>
+        <v>633998</v>
       </c>
       <c r="R4" t="n">
-        <v>7043362</v>
+        <v>7043532</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -972,7 +972,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ett tjugotal plantor</t>
+          <t>Flertal fruktkroppar</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113711370</v>
+        <v>113711366</v>
       </c>
       <c r="B5" t="n">
-        <v>91410</v>
+        <v>90331</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1015,25 +1015,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2059</v>
+        <v>1106</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1043,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>634063</v>
+        <v>634106</v>
       </c>
       <c r="R5" t="n">
-        <v>7043421</v>
+        <v>7043344</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1079,6 +1079,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-09-09</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,10 +1114,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113711373</v>
+        <v>113711376</v>
       </c>
       <c r="B6" t="n">
-        <v>81944</v>
+        <v>78794</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1125,21 +1130,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1149,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>634031</v>
+        <v>633976</v>
       </c>
       <c r="R6" t="n">
-        <v>7043487</v>
+        <v>7043552</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1215,10 +1220,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113711364</v>
+        <v>113711370</v>
       </c>
       <c r="B7" t="n">
-        <v>56955</v>
+        <v>91410</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1231,21 +1236,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>2059</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1255,10 +1260,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>634047</v>
+        <v>634063</v>
       </c>
       <c r="R7" t="n">
-        <v>7043456</v>
+        <v>7043421</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1291,11 +1296,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-09-09</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>I sitt häckningsrevir</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1326,10 +1326,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113711376</v>
+        <v>113711375</v>
       </c>
       <c r="B8" t="n">
-        <v>78794</v>
+        <v>56021</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1342,21 +1342,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>102612</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1366,10 +1366,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>633976</v>
+        <v>634006</v>
       </c>
       <c r="R8" t="n">
-        <v>7043552</v>
+        <v>7043583</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1402,6 +1402,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-09-09</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ett par i sitt revir</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1432,10 +1437,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113711377</v>
+        <v>113711373</v>
       </c>
       <c r="B9" t="n">
-        <v>91386</v>
+        <v>81944</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1448,21 +1453,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4361</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1472,10 +1477,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>633998</v>
+        <v>634031</v>
       </c>
       <c r="R9" t="n">
-        <v>7043532</v>
+        <v>7043487</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1508,11 +1513,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-09-09</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Flertal fruktkroppar</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1543,10 +1543,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113711368</v>
+        <v>113711369</v>
       </c>
       <c r="B10" t="n">
-        <v>56826</v>
+        <v>79265</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>634097</v>
+        <v>634071</v>
       </c>
       <c r="R10" t="n">
-        <v>7043390</v>
+        <v>7043394</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Hane i sitt födosöksområde</t>
+          <t>På stambasen av en sälg</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1654,10 +1654,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113711371</v>
+        <v>113711379</v>
       </c>
       <c r="B11" t="n">
-        <v>78236</v>
+        <v>91410</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1670,21 +1670,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>185</v>
+        <v>2059</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1694,10 +1694,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>634062</v>
+        <v>633985</v>
       </c>
       <c r="R11" t="n">
-        <v>7043422</v>
+        <v>7043541</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1760,10 +1760,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113711375</v>
+        <v>113711367</v>
       </c>
       <c r="B12" t="n">
-        <v>56021</v>
+        <v>97402</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1772,25 +1772,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1800,10 +1800,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>634006</v>
+        <v>634099</v>
       </c>
       <c r="R12" t="n">
-        <v>7043583</v>
+        <v>7043362</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ett par i sitt revir</t>
+          <t>Ett tjugotal plantor</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1871,10 +1871,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113711379</v>
+        <v>113711374</v>
       </c>
       <c r="B13" t="n">
-        <v>91410</v>
+        <v>79199</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1883,25 +1883,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2059</v>
+        <v>6456</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1911,10 +1911,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>633985</v>
+        <v>634019</v>
       </c>
       <c r="R13" t="n">
-        <v>7043541</v>
+        <v>7043512</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1947,6 +1947,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-09-09</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1977,10 +1982,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113711366</v>
+        <v>113711371</v>
       </c>
       <c r="B14" t="n">
-        <v>90331</v>
+        <v>78236</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1989,25 +1994,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1106</v>
+        <v>185</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2017,10 +2022,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>634106</v>
+        <v>634062</v>
       </c>
       <c r="R14" t="n">
-        <v>7043344</v>
+        <v>7043422</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2053,11 +2058,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-09-09</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2195,10 +2195,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113711372</v>
+        <v>113711368</v>
       </c>
       <c r="B16" t="n">
-        <v>97402</v>
+        <v>56826</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2207,25 +2207,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2235,10 +2235,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>634025</v>
+        <v>634097</v>
       </c>
       <c r="R16" t="n">
-        <v>7043472</v>
+        <v>7043390</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2275,7 +2275,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ett femtiotal plantor</t>
+          <t>Hane i sitt födosöksområde</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2306,10 +2306,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113711374</v>
+        <v>113711364</v>
       </c>
       <c r="B17" t="n">
-        <v>79199</v>
+        <v>56955</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2318,25 +2318,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6456</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2346,10 +2346,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>634019</v>
+        <v>634047</v>
       </c>
       <c r="R17" t="n">
-        <v>7043512</v>
+        <v>7043456</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På asp</t>
+          <t>I sitt häckningsrevir</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 50533-2023 artfynd.xlsx
+++ b/artfynd/A 50533-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113711372</v>
+        <v>113711365</v>
       </c>
       <c r="B2" t="n">
-        <v>97402</v>
+        <v>81944</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>634025</v>
+        <v>634113</v>
       </c>
       <c r="R2" t="n">
-        <v>7043472</v>
+        <v>7043339</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-09-09</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ett femtiotal plantor</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113711365</v>
+        <v>113711378</v>
       </c>
       <c r="B3" t="n">
-        <v>81944</v>
+        <v>91406</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>4366</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>634113</v>
+        <v>633994</v>
       </c>
       <c r="R3" t="n">
-        <v>7043339</v>
+        <v>7043512</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -870,6 +865,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -892,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113711377</v>
+        <v>113711376</v>
       </c>
       <c r="B4" t="n">
-        <v>91386</v>
+        <v>78794</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,21 +904,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4361</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>633998</v>
+        <v>633976</v>
       </c>
       <c r="R4" t="n">
-        <v>7043532</v>
+        <v>7043552</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -968,11 +964,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-09-09</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Flertal fruktkroppar</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,10 +994,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113711366</v>
+        <v>113711370</v>
       </c>
       <c r="B5" t="n">
-        <v>90331</v>
+        <v>91410</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1015,25 +1006,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1106</v>
+        <v>2059</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1043,10 +1034,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>634106</v>
+        <v>634063</v>
       </c>
       <c r="R5" t="n">
-        <v>7043344</v>
+        <v>7043421</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1079,11 +1070,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-09-09</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1114,10 +1100,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113711376</v>
+        <v>113711366</v>
       </c>
       <c r="B6" t="n">
-        <v>78794</v>
+        <v>90331</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1126,25 +1112,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>1106</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1154,10 +1140,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>633976</v>
+        <v>634106</v>
       </c>
       <c r="R6" t="n">
-        <v>7043552</v>
+        <v>7043344</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1190,6 +1176,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-09-09</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,10 +1211,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113711370</v>
+        <v>113711364</v>
       </c>
       <c r="B7" t="n">
-        <v>91410</v>
+        <v>56955</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1236,21 +1227,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2059</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1260,10 +1251,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>634063</v>
+        <v>634047</v>
       </c>
       <c r="R7" t="n">
-        <v>7043421</v>
+        <v>7043456</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1296,6 +1287,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-09-09</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>I sitt häckningsrevir</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1326,10 +1322,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113711375</v>
+        <v>113711377</v>
       </c>
       <c r="B8" t="n">
-        <v>56021</v>
+        <v>91386</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1342,21 +1338,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102612</v>
+        <v>4361</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1366,10 +1362,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>634006</v>
+        <v>633998</v>
       </c>
       <c r="R8" t="n">
-        <v>7043583</v>
+        <v>7043532</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1406,7 +1402,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ett par i sitt revir</t>
+          <t>Flertal fruktkroppar</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1437,10 +1433,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113711373</v>
+        <v>113711369</v>
       </c>
       <c r="B9" t="n">
-        <v>81944</v>
+        <v>79265</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1453,21 +1449,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1477,10 +1473,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>634031</v>
+        <v>634071</v>
       </c>
       <c r="R9" t="n">
-        <v>7043487</v>
+        <v>7043394</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1513,6 +1509,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-09-09</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På stambasen av en sälg</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1543,10 +1544,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113711369</v>
+        <v>113711379</v>
       </c>
       <c r="B10" t="n">
-        <v>79265</v>
+        <v>91410</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1559,21 +1560,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>2059</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1583,10 +1584,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>634071</v>
+        <v>633985</v>
       </c>
       <c r="R10" t="n">
-        <v>7043394</v>
+        <v>7043541</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1619,11 +1620,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-09-09</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På stambasen av en sälg</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1654,10 +1650,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113711379</v>
+        <v>113711368</v>
       </c>
       <c r="B11" t="n">
-        <v>91410</v>
+        <v>56826</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1670,21 +1666,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2059</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1694,10 +1690,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>633985</v>
+        <v>634097</v>
       </c>
       <c r="R11" t="n">
-        <v>7043541</v>
+        <v>7043390</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1730,6 +1726,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-09-09</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Hane i sitt födosöksområde</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1760,10 +1761,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113711367</v>
+        <v>113711375</v>
       </c>
       <c r="B12" t="n">
-        <v>97402</v>
+        <v>56021</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1772,25 +1773,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1800,10 +1801,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>634099</v>
+        <v>634006</v>
       </c>
       <c r="R12" t="n">
-        <v>7043362</v>
+        <v>7043583</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1840,7 +1841,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ett tjugotal plantor</t>
+          <t>Ett par i sitt revir</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1871,10 +1872,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113711374</v>
+        <v>113711367</v>
       </c>
       <c r="B13" t="n">
-        <v>79199</v>
+        <v>97402</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1883,25 +1884,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1911,10 +1912,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>634019</v>
+        <v>634099</v>
       </c>
       <c r="R13" t="n">
-        <v>7043512</v>
+        <v>7043362</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1951,7 +1952,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På asp</t>
+          <t>Ett tjugotal plantor</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1982,10 +1983,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113711371</v>
+        <v>113711374</v>
       </c>
       <c r="B14" t="n">
-        <v>78236</v>
+        <v>79199</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1994,25 +1995,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>185</v>
+        <v>6456</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2022,10 +2023,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>634062</v>
+        <v>634019</v>
       </c>
       <c r="R14" t="n">
-        <v>7043422</v>
+        <v>7043512</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2058,6 +2059,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-09-09</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2088,10 +2094,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113711378</v>
+        <v>113711373</v>
       </c>
       <c r="B15" t="n">
-        <v>91406</v>
+        <v>81944</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2100,25 +2106,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4366</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2128,10 +2134,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>633994</v>
+        <v>634031</v>
       </c>
       <c r="R15" t="n">
-        <v>7043512</v>
+        <v>7043487</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2172,7 +2178,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2195,10 +2200,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113711368</v>
+        <v>113711372</v>
       </c>
       <c r="B16" t="n">
-        <v>56826</v>
+        <v>97402</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2207,25 +2212,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2235,10 +2240,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>634097</v>
+        <v>634025</v>
       </c>
       <c r="R16" t="n">
-        <v>7043390</v>
+        <v>7043472</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2275,7 +2280,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Hane i sitt födosöksområde</t>
+          <t>Ett femtiotal plantor</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2306,10 +2311,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113711364</v>
+        <v>113711371</v>
       </c>
       <c r="B17" t="n">
-        <v>56955</v>
+        <v>78236</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2322,21 +2327,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>185</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2346,10 +2351,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>634047</v>
+        <v>634062</v>
       </c>
       <c r="R17" t="n">
-        <v>7043456</v>
+        <v>7043422</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2382,11 +2387,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-09-09</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>I sitt häckningsrevir</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 50533-2023 artfynd.xlsx
+++ b/artfynd/A 50533-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113711365</v>
+        <v>113711379</v>
       </c>
       <c r="B2" t="n">
-        <v>81944</v>
+        <v>91410</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>2059</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>634113</v>
+        <v>633985</v>
       </c>
       <c r="R2" t="n">
-        <v>7043339</v>
+        <v>7043541</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113711378</v>
+        <v>113711373</v>
       </c>
       <c r="B3" t="n">
-        <v>91406</v>
+        <v>81944</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4366</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>633994</v>
+        <v>634031</v>
       </c>
       <c r="R3" t="n">
-        <v>7043512</v>
+        <v>7043487</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -865,7 +865,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -888,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113711376</v>
+        <v>113711375</v>
       </c>
       <c r="B4" t="n">
-        <v>78794</v>
+        <v>56021</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>102612</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -928,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>633976</v>
+        <v>634006</v>
       </c>
       <c r="R4" t="n">
-        <v>7043552</v>
+        <v>7043583</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -964,6 +963,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-09-09</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ett par i sitt revir</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -994,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113711370</v>
+        <v>113711365</v>
       </c>
       <c r="B5" t="n">
-        <v>91410</v>
+        <v>81944</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1010,21 +1014,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2059</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1034,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>634063</v>
+        <v>634113</v>
       </c>
       <c r="R5" t="n">
-        <v>7043421</v>
+        <v>7043339</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1100,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113711366</v>
+        <v>113711372</v>
       </c>
       <c r="B6" t="n">
-        <v>90331</v>
+        <v>97402</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1116,21 +1120,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1106</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1140,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>634106</v>
+        <v>634025</v>
       </c>
       <c r="R6" t="n">
-        <v>7043344</v>
+        <v>7043472</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1180,7 +1184,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>Ett femtiotal plantor</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1211,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113711364</v>
+        <v>113711371</v>
       </c>
       <c r="B7" t="n">
-        <v>56955</v>
+        <v>78236</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1227,21 +1231,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1251,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>634047</v>
+        <v>634062</v>
       </c>
       <c r="R7" t="n">
-        <v>7043456</v>
+        <v>7043422</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1287,11 +1291,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-09-09</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>I sitt häckningsrevir</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1322,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113711377</v>
+        <v>113711364</v>
       </c>
       <c r="B8" t="n">
-        <v>91386</v>
+        <v>56955</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1338,21 +1337,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4361</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1362,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>633998</v>
+        <v>634047</v>
       </c>
       <c r="R8" t="n">
-        <v>7043532</v>
+        <v>7043456</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1402,7 +1401,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Flertal fruktkroppar</t>
+          <t>I sitt häckningsrevir</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1433,10 +1432,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113711369</v>
+        <v>113711376</v>
       </c>
       <c r="B9" t="n">
-        <v>79265</v>
+        <v>78794</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1449,21 +1448,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1473,10 +1472,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>634071</v>
+        <v>633976</v>
       </c>
       <c r="R9" t="n">
-        <v>7043394</v>
+        <v>7043552</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1509,11 +1508,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-09-09</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På stambasen av en sälg</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1544,10 +1538,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113711379</v>
+        <v>113711378</v>
       </c>
       <c r="B10" t="n">
-        <v>91410</v>
+        <v>91406</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1556,25 +1550,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2059</v>
+        <v>4366</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1584,10 +1578,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>633985</v>
+        <v>633994</v>
       </c>
       <c r="R10" t="n">
-        <v>7043541</v>
+        <v>7043512</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1628,6 +1622,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1650,10 +1645,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113711368</v>
+        <v>113711374</v>
       </c>
       <c r="B11" t="n">
-        <v>56826</v>
+        <v>79199</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1662,25 +1657,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6456</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1690,10 +1685,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>634097</v>
+        <v>634019</v>
       </c>
       <c r="R11" t="n">
-        <v>7043390</v>
+        <v>7043512</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1730,7 +1725,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Hane i sitt födosöksområde</t>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1761,10 +1756,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113711375</v>
+        <v>113711369</v>
       </c>
       <c r="B12" t="n">
-        <v>56021</v>
+        <v>79265</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1777,21 +1772,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1801,10 +1796,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>634006</v>
+        <v>634071</v>
       </c>
       <c r="R12" t="n">
-        <v>7043583</v>
+        <v>7043394</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1841,7 +1836,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ett par i sitt revir</t>
+          <t>På stambasen av en sälg</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1872,10 +1867,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113711367</v>
+        <v>113711368</v>
       </c>
       <c r="B13" t="n">
-        <v>97402</v>
+        <v>56826</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1884,25 +1879,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1912,10 +1907,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>634099</v>
+        <v>634097</v>
       </c>
       <c r="R13" t="n">
-        <v>7043362</v>
+        <v>7043390</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1952,7 +1947,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ett tjugotal plantor</t>
+          <t>Hane i sitt födosöksområde</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1983,10 +1978,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113711374</v>
+        <v>113711377</v>
       </c>
       <c r="B14" t="n">
-        <v>79199</v>
+        <v>91386</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1995,25 +1990,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6456</v>
+        <v>4361</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2023,10 +2018,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>634019</v>
+        <v>633998</v>
       </c>
       <c r="R14" t="n">
-        <v>7043512</v>
+        <v>7043532</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2063,7 +2058,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På asp</t>
+          <t>Flertal fruktkroppar</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2094,10 +2089,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113711373</v>
+        <v>113711370</v>
       </c>
       <c r="B15" t="n">
-        <v>81944</v>
+        <v>91410</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2110,21 +2105,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>2059</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2134,10 +2129,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>634031</v>
+        <v>634063</v>
       </c>
       <c r="R15" t="n">
-        <v>7043487</v>
+        <v>7043421</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2200,10 +2195,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113711372</v>
+        <v>113711366</v>
       </c>
       <c r="B16" t="n">
-        <v>97402</v>
+        <v>90331</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2216,21 +2211,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>1106</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2240,10 +2235,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>634025</v>
+        <v>634106</v>
       </c>
       <c r="R16" t="n">
-        <v>7043472</v>
+        <v>7043344</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2280,7 +2275,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ett femtiotal plantor</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2311,10 +2306,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113711371</v>
+        <v>113711367</v>
       </c>
       <c r="B17" t="n">
-        <v>78236</v>
+        <v>97402</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2323,25 +2318,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2351,10 +2346,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>634062</v>
+        <v>634099</v>
       </c>
       <c r="R17" t="n">
-        <v>7043422</v>
+        <v>7043362</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2387,6 +2382,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-09-09</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ett tjugotal plantor</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 50533-2023 artfynd.xlsx
+++ b/artfynd/A 50533-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 50533-2023 artfynd.xlsx
+++ b/artfynd/A 50533-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113711371</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113711366</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -980,6 +995,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113711365</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1081,6 +1101,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113711373</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113711363</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1283,6 +1313,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113711370</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1384,6 +1419,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113711379</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1490,6 +1530,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113711377</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1592,6 +1637,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113711378</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1693,6 +1743,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113711376</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1799,6 +1854,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113711374</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1905,6 +1965,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113711369</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2011,6 +2076,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113711368</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2117,6 +2187,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113711375</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2223,6 +2298,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113711364</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2329,6 +2409,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113711367</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2435,8 +2520,32 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113711372</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>